--- a/veterinarian_forms/011_puppy_questionnaire--veterinarian_forms.xlsx
+++ b/veterinarian_forms/011_puppy_questionnaire--veterinarian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1145,17 +1145,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>new_puppy_color_choices</t>
+          <t>new_puppy_age_group_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>young</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Young</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>young</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Adult</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Adult</t>
+          <t>Senior</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>senior</t>
+          <t>kitten</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Kitten</t>
         </is>
       </c>
     </row>
@@ -1218,29 +1218,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>kitten</t>
+          <t>old</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kitten</t>
+          <t>Old</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>new_puppy_age_group_choices</t>
+          <t>new_puppy_health_issues_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>old</t>
+          <t>heart_issues</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>Heart issues</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>heart_issues</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Heart issues</t>
+          <t>Cancer</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cancer</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -1286,29 +1286,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>obesity</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Allergies</t>
+          <t>Obesity</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>new_puppy_health_issues_choices</t>
+          <t>microchip_type_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>obesity</t>
+          <t>rfid</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Obesity</t>
+          <t>RFID</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>rfid</t>
+          <t>microchip</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RFID</t>
+          <t>Microchip</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>microchip</t>
+          <t>chip</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Microchip</t>
+          <t>Chip</t>
         </is>
       </c>
     </row>
@@ -1354,29 +1354,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>chip</t>
+          <t>implant</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chip</t>
+          <t>Implant</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>microchip_type_choices</t>
+          <t>microchip_status_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>implant</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Implant</t>
+          <t>Registered</t>
         </is>
       </c>
     </row>
@@ -1388,27 +1388,10 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>registered</t>
+          <t>unregistered</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
-        <is>
-          <t>Registered</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>microchip_status_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>unregistered</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
         <is>
           <t>Unregistered</t>
         </is>
